--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123782586</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123782586</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1321 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124979004</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>589641</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6933597</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124976610</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589784</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6933517</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124975245</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589602</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6933502</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124976556</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589770</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6933501</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124977337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589776</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6933450</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124976789</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589797</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6933488</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124975398</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589618</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6933524</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124975064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589629</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6933461</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124977975</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589846</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6933557</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124978978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589658</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6933580</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124973662</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589542</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6933604</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124979004</v>
+        <v>124975398</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,40 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589641</v>
+        <v>589618</v>
       </c>
       <c r="R3" t="n">
-        <v>6933597</v>
+        <v>6933524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976610</v>
+        <v>124976556</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589784</v>
+        <v>589770</v>
       </c>
       <c r="R4" t="n">
-        <v>6933517</v>
+        <v>6933501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1023,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124975245</v>
+        <v>124979004</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,31 +1038,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589602</v>
+        <v>589641</v>
       </c>
       <c r="R5" t="n">
-        <v>6933502</v>
+        <v>6933597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124976556</v>
+        <v>124976610</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1202,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589770</v>
+        <v>589784</v>
       </c>
       <c r="R6" t="n">
-        <v>6933501</v>
+        <v>6933517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1267,12 +1262,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1401,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124976789</v>
+        <v>124975245</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,31 +1408,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589797</v>
+        <v>589602</v>
       </c>
       <c r="R8" t="n">
-        <v>6933488</v>
+        <v>6933502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124975398</v>
+        <v>124976789</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,25 +1530,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589618</v>
+        <v>589797</v>
       </c>
       <c r="R9" t="n">
-        <v>6933524</v>
+        <v>6933488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124975064</v>
+        <v>124978978</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,47 +1647,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589629</v>
+        <v>589658</v>
       </c>
       <c r="R10" t="n">
-        <v>6933461</v>
+        <v>6933580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124977975</v>
+        <v>124975064</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,34 +1763,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589846</v>
+        <v>589629</v>
       </c>
       <c r="R11" t="n">
-        <v>6933557</v>
+        <v>6933461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124978978</v>
+        <v>124973662</v>
       </c>
       <c r="B12" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,38 +1880,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589658</v>
+        <v>589542</v>
       </c>
       <c r="R12" t="n">
-        <v>6933580</v>
+        <v>6933604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1958,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124973662</v>
+        <v>124977975</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,39 +2006,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589542</v>
+        <v>589846</v>
       </c>
       <c r="R13" t="n">
-        <v>6933604</v>
+        <v>6933557</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124975398</v>
+        <v>124976610</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589618</v>
+        <v>589784</v>
       </c>
       <c r="R3" t="n">
-        <v>6933524</v>
+        <v>6933517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976556</v>
+        <v>124975398</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589770</v>
+        <v>589618</v>
       </c>
       <c r="R4" t="n">
-        <v>6933501</v>
+        <v>6933524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124979004</v>
+        <v>124976556</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,40 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589641</v>
+        <v>589770</v>
       </c>
       <c r="R5" t="n">
-        <v>6933597</v>
+        <v>6933501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124976610</v>
+        <v>124973662</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1197,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589784</v>
+        <v>589542</v>
       </c>
       <c r="R6" t="n">
-        <v>6933517</v>
+        <v>6933604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1262,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124977337</v>
+        <v>124979004</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,31 +1282,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589776</v>
+        <v>589641</v>
       </c>
       <c r="R7" t="n">
-        <v>6933450</v>
+        <v>6933597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124975245</v>
+        <v>124978978</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,43 +1408,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589602</v>
+        <v>589658</v>
       </c>
       <c r="R8" t="n">
-        <v>6933502</v>
+        <v>6933580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124976789</v>
+        <v>124975064</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,31 +1520,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1563,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589797</v>
+        <v>589629</v>
       </c>
       <c r="R9" t="n">
-        <v>6933488</v>
+        <v>6933461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1608,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124978978</v>
+        <v>124977337</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,38 +1641,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589658</v>
+        <v>589776</v>
       </c>
       <c r="R10" t="n">
-        <v>6933580</v>
+        <v>6933450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1719,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124975064</v>
+        <v>124977975</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,43 +1767,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589629</v>
+        <v>589846</v>
       </c>
       <c r="R11" t="n">
-        <v>6933461</v>
+        <v>6933557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1836,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,7 +1863,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124973662</v>
+        <v>124975245</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1913,10 +1908,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589542</v>
+        <v>589602</v>
       </c>
       <c r="R12" t="n">
-        <v>6933604</v>
+        <v>6933502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1978,22 +1973,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124977975</v>
+        <v>124976789</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,38 +1997,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589846</v>
+        <v>589797</v>
       </c>
       <c r="R13" t="n">
-        <v>6933557</v>
+        <v>6933488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,12 +2090,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124975398</v>
+        <v>124976556</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589618</v>
+        <v>589770</v>
       </c>
       <c r="R4" t="n">
-        <v>6933524</v>
+        <v>6933501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124976556</v>
+        <v>124975398</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589770</v>
+        <v>589618</v>
       </c>
       <c r="R5" t="n">
-        <v>6933501</v>
+        <v>6933524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1136,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124976610</v>
+        <v>124973662</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589784</v>
+        <v>589542</v>
       </c>
       <c r="R3" t="n">
-        <v>6933517</v>
+        <v>6933604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976556</v>
+        <v>124977337</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589770</v>
+        <v>589776</v>
       </c>
       <c r="R4" t="n">
-        <v>6933501</v>
+        <v>6933450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124975398</v>
+        <v>124976610</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589618</v>
+        <v>589784</v>
       </c>
       <c r="R5" t="n">
-        <v>6933524</v>
+        <v>6933517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124973662</v>
+        <v>124975245</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1193,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589542</v>
+        <v>589602</v>
       </c>
       <c r="R6" t="n">
-        <v>6933604</v>
+        <v>6933502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1258,22 +1263,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124979004</v>
+        <v>124975398</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,40 +1287,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589641</v>
+        <v>589618</v>
       </c>
       <c r="R7" t="n">
-        <v>6933597</v>
+        <v>6933524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,12 +1380,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1508,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124975064</v>
+        <v>124977975</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,43 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589629</v>
+        <v>589846</v>
       </c>
       <c r="R9" t="n">
-        <v>6933461</v>
+        <v>6933557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124977337</v>
+        <v>124976789</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,31 +1628,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1674,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589776</v>
+        <v>589797</v>
       </c>
       <c r="R10" t="n">
-        <v>6933450</v>
+        <v>6933488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,12 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,22 +1721,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124977975</v>
+        <v>124975064</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,34 +1749,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589846</v>
+        <v>589629</v>
       </c>
       <c r="R11" t="n">
-        <v>6933557</v>
+        <v>6933461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,7 +1854,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124975245</v>
+        <v>124976556</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1908,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589602</v>
+        <v>589770</v>
       </c>
       <c r="R12" t="n">
-        <v>6933502</v>
+        <v>6933501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1973,19 +1964,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124976789</v>
+        <v>124979004</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2018,10 +2009,19 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589797</v>
+        <v>589641</v>
       </c>
       <c r="R13" t="n">
-        <v>6933488</v>
+        <v>6933597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,12 +2090,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124973662</v>
+        <v>124975064</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,10 +820,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589542</v>
+        <v>589629</v>
       </c>
       <c r="R3" t="n">
-        <v>6933604</v>
+        <v>6933461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124977337</v>
+        <v>124976789</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +920,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589776</v>
+        <v>589797</v>
       </c>
       <c r="R4" t="n">
-        <v>6933450</v>
+        <v>6933488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124976610</v>
+        <v>124975245</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1076,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589784</v>
+        <v>589602</v>
       </c>
       <c r="R5" t="n">
-        <v>6933517</v>
+        <v>6933502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124975245</v>
+        <v>124978978</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,43 +1159,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589602</v>
+        <v>589658</v>
       </c>
       <c r="R6" t="n">
-        <v>6933502</v>
+        <v>6933580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124975398</v>
+        <v>124973662</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,16 +1275,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1295,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589618</v>
+        <v>589542</v>
       </c>
       <c r="R7" t="n">
-        <v>6933524</v>
+        <v>6933604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124978978</v>
+        <v>124976556</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,38 +1393,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589658</v>
+        <v>589770</v>
       </c>
       <c r="R8" t="n">
-        <v>6933580</v>
+        <v>6933501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124977975</v>
+        <v>124977337</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1519,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589846</v>
+        <v>589776</v>
       </c>
       <c r="R9" t="n">
-        <v>6933557</v>
+        <v>6933450</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1593,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976789</v>
+        <v>124976610</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,31 +1637,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1661,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589797</v>
+        <v>589784</v>
       </c>
       <c r="R10" t="n">
-        <v>6933488</v>
+        <v>6933517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1715,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124975064</v>
+        <v>124979004</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,25 +1759,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1771,9 +1785,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1782,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589629</v>
+        <v>589641</v>
       </c>
       <c r="R11" t="n">
-        <v>6933461</v>
+        <v>6933597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1836,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1846,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124976556</v>
+        <v>124975398</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,16 +1889,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1890,7 +1909,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,10 +1918,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589770</v>
+        <v>589618</v>
       </c>
       <c r="R12" t="n">
-        <v>6933501</v>
+        <v>6933524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1953,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,12 +1963,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,22 +1978,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124979004</v>
+        <v>124977975</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,52 +2002,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589641</v>
+        <v>589846</v>
       </c>
       <c r="R13" t="n">
-        <v>6933597</v>
+        <v>6933557</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124975064</v>
+        <v>124977337</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,14 +820,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589629</v>
+        <v>589776</v>
       </c>
       <c r="R3" t="n">
-        <v>6933461</v>
+        <v>6933450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976789</v>
+        <v>124975064</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +921,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589797</v>
+        <v>589629</v>
       </c>
       <c r="R4" t="n">
-        <v>6933488</v>
+        <v>6933461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1018,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124975245</v>
+        <v>124976610</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1070,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589602</v>
+        <v>589784</v>
       </c>
       <c r="R5" t="n">
-        <v>6933502</v>
+        <v>6933517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124978978</v>
+        <v>124975245</v>
       </c>
       <c r="B6" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,38 +1164,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589658</v>
+        <v>589602</v>
       </c>
       <c r="R6" t="n">
-        <v>6933580</v>
+        <v>6933502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1262,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124973662</v>
+        <v>124976789</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1286,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589542</v>
+        <v>589797</v>
       </c>
       <c r="R7" t="n">
-        <v>6933604</v>
+        <v>6933488</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124976556</v>
+        <v>124979004</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,31 +1403,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589770</v>
+        <v>589641</v>
       </c>
       <c r="R8" t="n">
-        <v>6933501</v>
+        <v>6933597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124977337</v>
+        <v>124975398</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,16 +1533,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,7 +1553,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589776</v>
+        <v>589618</v>
       </c>
       <c r="R9" t="n">
-        <v>6933450</v>
+        <v>6933524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,12 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,19 +1622,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976610</v>
+        <v>124973662</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1670,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589784</v>
+        <v>589542</v>
       </c>
       <c r="R10" t="n">
-        <v>6933517</v>
+        <v>6933604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1714,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1724,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1735,22 +1744,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124979004</v>
+        <v>124976556</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,40 +1768,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589641</v>
+        <v>589770</v>
       </c>
       <c r="R11" t="n">
-        <v>6933597</v>
+        <v>6933501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1846,7 +1846,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1878,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124975398</v>
+        <v>124977975</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,39 +1894,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589618</v>
+        <v>589846</v>
       </c>
       <c r="R12" t="n">
-        <v>6933524</v>
+        <v>6933557</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,22 +1978,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124977975</v>
+        <v>124978978</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,25 +2002,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589846</v>
+        <v>589658</v>
       </c>
       <c r="R13" t="n">
-        <v>6933557</v>
+        <v>6933580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124977337</v>
+        <v>124975398</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589776</v>
+        <v>589618</v>
       </c>
       <c r="R3" t="n">
-        <v>6933450</v>
+        <v>6933524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124975064</v>
+        <v>124973662</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,14 +937,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589629</v>
+        <v>589542</v>
       </c>
       <c r="R4" t="n">
-        <v>6933461</v>
+        <v>6933604</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124976610</v>
+        <v>124977975</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589784</v>
+        <v>589846</v>
       </c>
       <c r="R5" t="n">
-        <v>6933517</v>
+        <v>6933557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124975245</v>
+        <v>124979004</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,31 +1150,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1197,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589602</v>
+        <v>589641</v>
       </c>
       <c r="R6" t="n">
-        <v>6933502</v>
+        <v>6933597</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124976789</v>
+        <v>124978978</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98122</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589797</v>
+        <v>589658</v>
       </c>
       <c r="R7" t="n">
-        <v>6933488</v>
+        <v>6933580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124979004</v>
+        <v>124975064</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1429,14 +1414,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1445,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589641</v>
+        <v>589629</v>
       </c>
       <c r="R8" t="n">
-        <v>6933597</v>
+        <v>6933461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124975398</v>
+        <v>124976610</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1553,7 +1533,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1562,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589618</v>
+        <v>589784</v>
       </c>
       <c r="R9" t="n">
-        <v>6933524</v>
+        <v>6933517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124973662</v>
+        <v>124975245</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1679,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589542</v>
+        <v>589602</v>
       </c>
       <c r="R10" t="n">
-        <v>6933604</v>
+        <v>6933502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1744,22 +1729,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976556</v>
+        <v>124976789</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,31 +1753,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1801,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589770</v>
+        <v>589797</v>
       </c>
       <c r="R11" t="n">
-        <v>6933501</v>
+        <v>6933488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,7 +1821,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1846,12 +1831,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,22 +1846,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124977975</v>
+        <v>124976556</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,34 +1874,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589846</v>
+        <v>589770</v>
       </c>
       <c r="R12" t="n">
-        <v>6933557</v>
+        <v>6933501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,7 +1948,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,10 +1980,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124978978</v>
+        <v>124977337</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,38 +1992,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589658</v>
+        <v>589776</v>
       </c>
       <c r="R13" t="n">
-        <v>6933580</v>
+        <v>6933450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124975398</v>
+        <v>124976556</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589618</v>
+        <v>589770</v>
       </c>
       <c r="R3" t="n">
-        <v>6933524</v>
+        <v>6933501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124973662</v>
+        <v>124975245</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589542</v>
+        <v>589602</v>
       </c>
       <c r="R4" t="n">
-        <v>6933604</v>
+        <v>6933502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1014,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124977975</v>
+        <v>124973662</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1047,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589846</v>
+        <v>589542</v>
       </c>
       <c r="R5" t="n">
-        <v>6933557</v>
+        <v>6933604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124979004</v>
+        <v>124975398</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,40 +1165,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589641</v>
+        <v>589618</v>
       </c>
       <c r="R6" t="n">
-        <v>6933597</v>
+        <v>6933524</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124978978</v>
+        <v>124977337</v>
       </c>
       <c r="B7" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,38 +1282,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589658</v>
+        <v>589776</v>
       </c>
       <c r="R7" t="n">
-        <v>6933580</v>
+        <v>6933450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124975064</v>
+        <v>124976610</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,16 +1408,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1409,14 +1425,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1425,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589629</v>
+        <v>589784</v>
       </c>
       <c r="R8" t="n">
-        <v>6933461</v>
+        <v>6933517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,22 +1502,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124976610</v>
+        <v>124977975</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,39 +1530,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589784</v>
+        <v>589846</v>
       </c>
       <c r="R9" t="n">
-        <v>6933517</v>
+        <v>6933557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,22 +1614,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124975245</v>
+        <v>124976789</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,31 +1638,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1664,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589602</v>
+        <v>589797</v>
       </c>
       <c r="R10" t="n">
-        <v>6933502</v>
+        <v>6933488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976789</v>
+        <v>124978978</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,39 +1759,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589797</v>
+        <v>589658</v>
       </c>
       <c r="R11" t="n">
-        <v>6933488</v>
+        <v>6933580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,22 +1843,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124976556</v>
+        <v>124979004</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,31 +1867,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1903,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589770</v>
+        <v>589641</v>
       </c>
       <c r="R12" t="n">
-        <v>6933501</v>
+        <v>6933597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,12 +1954,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124977337</v>
+        <v>124975064</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,16 +1997,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2013,10 +2014,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2025,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589776</v>
+        <v>589629</v>
       </c>
       <c r="R13" t="n">
-        <v>6933450</v>
+        <v>6933461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124975245</v>
+        <v>124975398</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589602</v>
+        <v>589618</v>
       </c>
       <c r="R4" t="n">
-        <v>6933502</v>
+        <v>6933524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1153,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124975398</v>
+        <v>124978978</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>98122</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,43 +1160,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589618</v>
+        <v>589658</v>
       </c>
       <c r="R6" t="n">
-        <v>6933524</v>
+        <v>6933580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124977337</v>
+        <v>124976789</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,31 +1272,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589776</v>
+        <v>589797</v>
       </c>
       <c r="R7" t="n">
-        <v>6933450</v>
+        <v>6933488</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,19 +1365,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124976610</v>
+        <v>124977337</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1437,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589784</v>
+        <v>589776</v>
       </c>
       <c r="R8" t="n">
-        <v>6933517</v>
+        <v>6933450</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1502,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124977975</v>
+        <v>124976610</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,34 +1515,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589846</v>
+        <v>589784</v>
       </c>
       <c r="R9" t="n">
-        <v>6933557</v>
+        <v>6933517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,19 +1609,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976789</v>
+        <v>124979004</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1659,10 +1654,19 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589797</v>
+        <v>589641</v>
       </c>
       <c r="R10" t="n">
-        <v>6933488</v>
+        <v>6933597</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,22 +1735,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124978978</v>
+        <v>124975245</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,38 +1759,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589658</v>
+        <v>589602</v>
       </c>
       <c r="R11" t="n">
-        <v>6933580</v>
+        <v>6933502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1837,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,22 +1857,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124979004</v>
+        <v>124975064</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,25 +1881,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1893,14 +1907,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1909,10 +1918,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589641</v>
+        <v>589629</v>
       </c>
       <c r="R12" t="n">
-        <v>6933597</v>
+        <v>6933461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1953,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,7 +1963,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124975064</v>
+        <v>124977975</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,43 +2006,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589629</v>
+        <v>589846</v>
       </c>
       <c r="R13" t="n">
-        <v>6933461</v>
+        <v>6933557</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124976556</v>
+        <v>124973662</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589770</v>
+        <v>589542</v>
       </c>
       <c r="R3" t="n">
-        <v>6933501</v>
+        <v>6933604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124975398</v>
+        <v>124976610</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589618</v>
+        <v>589784</v>
       </c>
       <c r="R4" t="n">
-        <v>6933524</v>
+        <v>6933517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124973662</v>
+        <v>124977337</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1071,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589542</v>
+        <v>589776</v>
       </c>
       <c r="R5" t="n">
-        <v>6933604</v>
+        <v>6933450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1148,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124978978</v>
+        <v>124979004</v>
       </c>
       <c r="B6" t="n">
-        <v>98122</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1169,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589658</v>
+        <v>589641</v>
       </c>
       <c r="R6" t="n">
-        <v>6933580</v>
+        <v>6933597</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124977337</v>
+        <v>124975245</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1422,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589776</v>
+        <v>589602</v>
       </c>
       <c r="R8" t="n">
-        <v>6933450</v>
+        <v>6933502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1487,22 +1506,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124976610</v>
+        <v>124975064</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,16 +1534,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1532,10 +1551,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1544,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589784</v>
+        <v>589629</v>
       </c>
       <c r="R9" t="n">
-        <v>6933517</v>
+        <v>6933461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,22 +1627,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124979004</v>
+        <v>124975398</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,40 +1651,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1675,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589641</v>
+        <v>589618</v>
       </c>
       <c r="R10" t="n">
-        <v>6933597</v>
+        <v>6933524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,22 +1744,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124975245</v>
+        <v>124978978</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,43 +1768,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589602</v>
+        <v>589658</v>
       </c>
       <c r="R11" t="n">
-        <v>6933502</v>
+        <v>6933580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,12 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,22 +1856,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124975064</v>
+        <v>124976556</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,16 +1884,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1902,14 +1901,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589629</v>
+        <v>589770</v>
       </c>
       <c r="R12" t="n">
-        <v>6933461</v>
+        <v>6933501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,7 +1958,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976610</v>
+        <v>124977337</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589784</v>
+        <v>589776</v>
       </c>
       <c r="R4" t="n">
-        <v>6933517</v>
+        <v>6933450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124977337</v>
+        <v>124976610</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589776</v>
+        <v>589784</v>
       </c>
       <c r="R5" t="n">
-        <v>6933450</v>
+        <v>6933517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1141,12 +1141,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124973662</v>
+        <v>124978978</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589542</v>
+        <v>589658</v>
       </c>
       <c r="R3" t="n">
-        <v>6933604</v>
+        <v>6933580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124976610</v>
+        <v>124979004</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1033,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589784</v>
+        <v>589641</v>
       </c>
       <c r="R5" t="n">
-        <v>6933517</v>
+        <v>6933597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124979004</v>
+        <v>124977975</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,52 +1159,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589641</v>
+        <v>589846</v>
       </c>
       <c r="R6" t="n">
-        <v>6933597</v>
+        <v>6933557</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124976789</v>
+        <v>124973662</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,31 +1271,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589797</v>
+        <v>589542</v>
       </c>
       <c r="R7" t="n">
-        <v>6933488</v>
+        <v>6933604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,12 +1369,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1518,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124975064</v>
+        <v>124976610</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,16 +1519,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1551,14 +1536,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589629</v>
+        <v>589784</v>
       </c>
       <c r="R9" t="n">
-        <v>6933461</v>
+        <v>6933517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1593,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,22 +1613,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124975398</v>
+        <v>124976556</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,16 +1641,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1675,7 +1661,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1684,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589618</v>
+        <v>589770</v>
       </c>
       <c r="R10" t="n">
-        <v>6933524</v>
+        <v>6933501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1715,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,22 +1735,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124978978</v>
+        <v>124975064</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,38 +1759,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589658</v>
+        <v>589629</v>
       </c>
       <c r="R11" t="n">
-        <v>6933580</v>
+        <v>6933461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124976556</v>
+        <v>124976789</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,31 +1880,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589770</v>
+        <v>589797</v>
       </c>
       <c r="R12" t="n">
-        <v>6933501</v>
+        <v>6933488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,12 +1958,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,22 +1973,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124977975</v>
+        <v>124975398</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2006,34 +2001,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589846</v>
+        <v>589618</v>
       </c>
       <c r="R13" t="n">
-        <v>6933557</v>
+        <v>6933524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,12 +2090,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124978978</v>
+        <v>124973662</v>
       </c>
       <c r="B3" t="n">
-        <v>98122</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589658</v>
+        <v>589542</v>
       </c>
       <c r="R3" t="n">
-        <v>6933580</v>
+        <v>6933604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124977337</v>
+        <v>124976789</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +921,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589776</v>
+        <v>589797</v>
       </c>
       <c r="R4" t="n">
-        <v>6933450</v>
+        <v>6933488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124979004</v>
+        <v>124977337</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,40 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589641</v>
+        <v>589776</v>
       </c>
       <c r="R5" t="n">
-        <v>6933597</v>
+        <v>6933450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124977975</v>
+        <v>124976610</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589846</v>
+        <v>589784</v>
       </c>
       <c r="R6" t="n">
-        <v>6933557</v>
+        <v>6933517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124973662</v>
+        <v>124978978</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,43 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589542</v>
+        <v>589658</v>
       </c>
       <c r="R7" t="n">
-        <v>6933604</v>
+        <v>6933580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124975245</v>
+        <v>124975064</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,16 +1398,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1414,10 +1415,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589602</v>
+        <v>589629</v>
       </c>
       <c r="R8" t="n">
-        <v>6933502</v>
+        <v>6933461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,11 +1479,6 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1491,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124976610</v>
+        <v>124979004</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,31 +1515,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589784</v>
+        <v>589641</v>
       </c>
       <c r="R9" t="n">
-        <v>6933517</v>
+        <v>6933597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,12 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976556</v>
+        <v>124975398</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,16 +1645,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1661,7 +1665,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589770</v>
+        <v>589618</v>
       </c>
       <c r="R10" t="n">
-        <v>6933501</v>
+        <v>6933524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,12 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,22 +1734,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124975064</v>
+        <v>124976556</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,16 +1762,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1780,14 +1779,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1796,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589629</v>
+        <v>589770</v>
       </c>
       <c r="R11" t="n">
-        <v>6933461</v>
+        <v>6933501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1836,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124976789</v>
+        <v>124977975</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,43 +1880,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589797</v>
+        <v>589846</v>
       </c>
       <c r="R12" t="n">
-        <v>6933488</v>
+        <v>6933557</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,22 +1968,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124975398</v>
+        <v>124975245</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2001,16 +1996,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2021,7 +2016,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2030,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589618</v>
+        <v>589602</v>
       </c>
       <c r="R13" t="n">
-        <v>6933524</v>
+        <v>6933502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124973662</v>
+        <v>124976556</v>
       </c>
       <c r="B3" t="n">
         <v>57635</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589542</v>
+        <v>589770</v>
       </c>
       <c r="R3" t="n">
-        <v>6933604</v>
+        <v>6933501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976789</v>
+        <v>124975064</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
+        <v>56828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589797</v>
+        <v>589629</v>
       </c>
       <c r="R4" t="n">
-        <v>6933488</v>
+        <v>6933461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124977337</v>
+        <v>124975398</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,7 +1066,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589776</v>
+        <v>589618</v>
       </c>
       <c r="R5" t="n">
-        <v>6933450</v>
+        <v>6933524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1135,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124976610</v>
+        <v>124977337</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1193,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589784</v>
+        <v>589776</v>
       </c>
       <c r="R6" t="n">
-        <v>6933517</v>
+        <v>6933450</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1258,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124978978</v>
+        <v>124979004</v>
       </c>
       <c r="B7" t="n">
-        <v>98290</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1285,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589658</v>
+        <v>589641</v>
       </c>
       <c r="R7" t="n">
-        <v>6933580</v>
+        <v>6933597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124975064</v>
+        <v>124976610</v>
       </c>
       <c r="B8" t="n">
-        <v>56828</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1411,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1415,14 +1428,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589629</v>
+        <v>589784</v>
       </c>
       <c r="R8" t="n">
-        <v>6933461</v>
+        <v>6933517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1505,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124979004</v>
+        <v>124977975</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,52 +1529,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589641</v>
+        <v>589846</v>
       </c>
       <c r="R9" t="n">
-        <v>6933597</v>
+        <v>6933557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124975398</v>
+        <v>124976789</v>
       </c>
       <c r="B10" t="n">
-        <v>56828</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589618</v>
+        <v>589797</v>
       </c>
       <c r="R10" t="n">
-        <v>6933524</v>
+        <v>6933488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124976556</v>
+        <v>124975245</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589770</v>
+        <v>589602</v>
       </c>
       <c r="R11" t="n">
-        <v>6933501</v>
+        <v>6933502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1856,22 +1856,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124977975</v>
+        <v>124978978</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>98290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,25 +1880,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589846</v>
+        <v>589658</v>
       </c>
       <c r="R12" t="n">
-        <v>6933557</v>
+        <v>6933580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124975245</v>
+        <v>124973662</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589602</v>
+        <v>589542</v>
       </c>
       <c r="R13" t="n">
-        <v>6933502</v>
+        <v>6933604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2090,12 +2090,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -787,16 +787,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124976556</v>
+        <v>124975245</v>
       </c>
       <c r="B3" t="n">
         <v>57635</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589770</v>
+        <v>589602</v>
       </c>
       <c r="R3" t="n">
-        <v>6933501</v>
+        <v>6933502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,27 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124975064</v>
+        <v>124976556</v>
       </c>
       <c r="B4" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,14 +932,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589629</v>
+        <v>589770</v>
       </c>
       <c r="R4" t="n">
-        <v>6933461</v>
+        <v>6933501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,16 +1021,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124975398</v>
+        <v>124975064</v>
       </c>
       <c r="B5" t="n">
         <v>56828</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1063,10 +1049,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589618</v>
+        <v>589629</v>
       </c>
       <c r="R5" t="n">
-        <v>6933524</v>
+        <v>6933461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,55 +1125,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124977337</v>
+        <v>124976789</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589776</v>
+        <v>589797</v>
       </c>
       <c r="R6" t="n">
-        <v>6933450</v>
+        <v>6933488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,64 +1237,50 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124979004</v>
+        <v>124976610</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1323,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589641</v>
+        <v>589784</v>
       </c>
       <c r="R7" t="n">
-        <v>6933597</v>
+        <v>6933517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1334,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,28 +1354,23 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124976610</v>
+        <v>124977337</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1440,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589784</v>
+        <v>589776</v>
       </c>
       <c r="R8" t="n">
-        <v>6933517</v>
+        <v>6933450</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1505,27 +1471,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124977975</v>
+        <v>124975398</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589846</v>
+        <v>589618</v>
       </c>
       <c r="R9" t="n">
-        <v>6933557</v>
+        <v>6933524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,55 +1583,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124976789</v>
+        <v>124973662</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1674,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589797</v>
+        <v>589542</v>
       </c>
       <c r="R10" t="n">
-        <v>6933488</v>
+        <v>6933604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,55 +1700,59 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124975245</v>
+        <v>124979004</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1791,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589602</v>
+        <v>589641</v>
       </c>
       <c r="R11" t="n">
-        <v>6933502</v>
+        <v>6933597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,12 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,12 +1821,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1873,11 +1838,6 @@
       <c r="B12" t="n">
         <v>98290</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1980,15 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124973662</v>
+        <v>124977975</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,39 +1951,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589542</v>
+        <v>589846</v>
       </c>
       <c r="R13" t="n">
-        <v>6933604</v>
+        <v>6933557</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>124975245</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>124976556</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>124976610</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>124977337</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>124973662</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>124975245</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>124976556</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>124976610</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>124977337</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>124973662</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123782586</v>
+        <v>103694333</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Högsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589408</v>
+        <v>589436</v>
       </c>
       <c r="R2" t="n">
-        <v>6933586</v>
+        <v>6933519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124975245</v>
+        <v>123782498</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverbäcken, Näverbäcken, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589602</v>
+        <v>589393</v>
       </c>
       <c r="R3" t="n">
-        <v>6933502</v>
+        <v>6933577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124976556</v>
+        <v>123782586</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näverbäcken, Näverbäcken, Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589770</v>
+        <v>589408</v>
       </c>
       <c r="R4" t="n">
-        <v>6933501</v>
+        <v>6933586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,27 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124975064</v>
+        <v>124977975</v>
       </c>
       <c r="B5" t="n">
-        <v>56828</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,43 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589629</v>
+        <v>589846</v>
       </c>
       <c r="R5" t="n">
-        <v>6933461</v>
+        <v>6933557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124976789</v>
+        <v>124978062</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589797</v>
+        <v>589867</v>
       </c>
       <c r="R6" t="n">
-        <v>6933488</v>
+        <v>6933550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124976610</v>
+        <v>124973662</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589784</v>
+        <v>589542</v>
       </c>
       <c r="R7" t="n">
-        <v>6933517</v>
+        <v>6933604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1265,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1275,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1354,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124977337</v>
+        <v>124975245</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589776</v>
+        <v>589602</v>
       </c>
       <c r="R8" t="n">
-        <v>6933450</v>
+        <v>6933502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1471,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124975398</v>
+        <v>124976556</v>
       </c>
       <c r="B9" t="n">
-        <v>56828</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,16 +1435,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,7 +1455,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1523,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589618</v>
+        <v>589770</v>
       </c>
       <c r="R9" t="n">
-        <v>6933524</v>
+        <v>6933501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124973662</v>
+        <v>124976610</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589542</v>
+        <v>589784</v>
       </c>
       <c r="R10" t="n">
-        <v>6933604</v>
+        <v>6933517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1700,59 +1646,50 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124979004</v>
+        <v>124977337</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1761,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589641</v>
+        <v>589776</v>
       </c>
       <c r="R11" t="n">
-        <v>6933597</v>
+        <v>6933450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1743,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124978978</v>
+        <v>124976789</v>
       </c>
       <c r="B12" t="n">
-        <v>98290</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,34 +1786,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589658</v>
+        <v>589797</v>
       </c>
       <c r="R12" t="n">
-        <v>6933580</v>
+        <v>6933488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,57 +1875,71 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124977975</v>
+        <v>124979004</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbäcken, Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589846</v>
+        <v>589641</v>
       </c>
       <c r="R13" t="n">
-        <v>6933557</v>
+        <v>6933597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,6 +2005,341 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124975064</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589629</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6933461</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124975398</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589618</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6933524</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124978978</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589658</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6933580</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4865-2025 artfynd.xlsx
+++ b/artfynd/A 4865-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694333</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123782498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123782586</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124973662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124975245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124979004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124975064</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124975398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124977975</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124978062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124976556</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124976610</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2121,6 +2186,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124977337</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124976789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,8 +2415,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124978978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>